--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-06-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ACB959-B43A-41A4-938E-07D40FFFC56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3551A3-40F7-4947-B48E-8399396DCC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31785" yWindow="1185" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31830" yWindow="2115" windowWidth="21600" windowHeight="14295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1894,7 +1894,7 @@
         <v>80</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="s">
         <v>81</v>
